--- a/outputs/llm_eval/test_yjx/mul/two_turns/test4_correlation_results.xlsx
+++ b/outputs/llm_eval/test_yjx/mul/two_turns/test4_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.5093389058756876</v>
+        <v>0.4638263099688042</v>
       </c>
       <c r="C2">
-        <v>0.670012190156863</v>
+        <v>0.565186813730484</v>
       </c>
       <c r="D2">
-        <v>0.4574626332592572</v>
+        <v>0.4335435275684837</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.4489522177309438</v>
+        <v>0.4580484081081715</v>
       </c>
       <c r="C3">
-        <v>0.5605574648594245</v>
+        <v>0.5595352766529627</v>
       </c>
       <c r="D3">
-        <v>0.3710024185984432</v>
+        <v>0.4098389567801684</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,13 +445,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.4498322772047478</v>
+        <v>0.3080834349299427</v>
       </c>
       <c r="C4">
-        <v>0.4704507795774038</v>
+        <v>0.3137524965013466</v>
       </c>
       <c r="D4">
-        <v>0.3692906887820909</v>
+        <v>0.2575028121480921</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -459,13 +459,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.528633498128241</v>
+        <v>0.4488437304907142</v>
       </c>
       <c r="C5">
-        <v>0.5828842758787601</v>
+        <v>0.4874061672702376</v>
       </c>
       <c r="D5">
-        <v>0.4408906449910345</v>
+        <v>0.3847265639072598</v>
       </c>
     </row>
   </sheetData>
